--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-datasetseries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://healthri.sharepoint.com/sites/hri-team012/Shared Documents/A-Team/26 - Implementation/50 - Technical/V2 Shapes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://healthri-my.sharepoint.com/personal/hannah_neikes_health-ri_nl/Documents/Documenten/GitHub/health-ri-metadata/Formalisation(shacl)/Core/SHACL_pipeline_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="13_ncr:1_{CC90F1A9-7F52-8148-BE94-617DCF70111C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF5233DE-1FD7-A74E-B439-C1E027ED1481}"/>
+  <xr:revisionPtr revIDLastSave="213" documentId="13_ncr:1_{CC90F1A9-7F52-8148-BE94-617DCF70111C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80C40141-C6AB-42B2-9B84-BED41E8B7969}"/>
   <bookViews>
-    <workbookView xWindow="-17720" yWindow="-28300" windowWidth="36000" windowHeight="22500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5316" yWindow="-15924" windowWidth="23040" windowHeight="13560" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prefixes" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="181">
   <si>
     <t>PREFIX</t>
   </si>
@@ -576,6 +576,15 @@
   </si>
   <si>
     <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
+  </si>
+  <si>
+    <t>dcat:seriesMember</t>
+  </si>
+  <si>
+    <t>series member</t>
+  </si>
+  <si>
+    <t>This is an inverse property of the Dataset's *dcat:inSeries* property. It can be used to show which Datasets are part of a Dataset Series. Note that this inverse **may** be used in addition to the *dcat:inSeries* (in Dataset class), but must not be used to replace it. So the connection between Datasets and Series still has to run primarily via the *dcat:inSeries*.</t>
   </si>
 </sst>
 </file>
@@ -1605,7 +1614,6 @@
     <cellStyle name="Neutre 2 2" xfId="126" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
     <cellStyle name="Neutre 3" xfId="127" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
     <cellStyle name="Neutre 3 2" xfId="128" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="129" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
     <cellStyle name="Normal 2" xfId="130" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
     <cellStyle name="Normal 2 2" xfId="131" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
@@ -1632,6 +1640,7 @@
     <cellStyle name="Normal 9 3" xfId="152" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
     <cellStyle name="Note 17" xfId="153" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
     <cellStyle name="Result (user) 18" xfId="154" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
     <cellStyle name="Status 19" xfId="155" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
     <cellStyle name="Text 20" xfId="156" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
     <cellStyle name="Titre 2" xfId="157" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
@@ -1848,13 +1857,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="59.5" customWidth="1"/>
+    <col min="3" max="3" width="59.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1865,7 +1874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1876,7 +1885,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1887,7 +1896,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1898,7 +1907,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1909,7 +1918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -1920,7 +1929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -1931,7 +1940,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -1942,7 +1951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -1953,7 +1962,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1964,7 +1973,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -1975,7 +1984,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -1986,7 +1995,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -1997,7 +2006,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -2008,7 +2017,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -2019,7 +2028,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="48" t="s">
         <v>0</v>
       </c>
@@ -2030,7 +2039,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="48" t="s">
         <v>0</v>
       </c>
@@ -2041,7 +2050,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="48" t="s">
         <v>0</v>
       </c>
@@ -2052,7 +2061,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="48" t="s">
         <v>0</v>
       </c>
@@ -2063,7 +2072,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="48" t="s">
         <v>0</v>
       </c>
@@ -2074,7 +2083,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="48" t="s">
         <v>0</v>
       </c>
@@ -2116,24 +2125,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" customWidth="1"/>
     <col min="3" max="3" width="42.33203125" customWidth="1"/>
-    <col min="4" max="5" width="38.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="4" max="5" width="38.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
     <col min="7" max="7" width="25.33203125" style="5" customWidth="1"/>
     <col min="8" max="8" width="16.33203125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="31.1640625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="31.109375" style="5" customWidth="1"/>
     <col min="10" max="10" width="52" customWidth="1"/>
     <col min="11" max="11" width="40" style="5" customWidth="1"/>
-    <col min="12" max="12" width="20.5" customWidth="1"/>
+    <col min="12" max="12" width="20.44140625" customWidth="1"/>
     <col min="13" max="13" width="27.33203125" customWidth="1"/>
-    <col min="1014" max="1018" width="11.5" customWidth="1"/>
+    <col min="1014" max="1018" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -2142,7 +2151,7 @@
       </c>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -2151,7 +2160,7 @@
       </c>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -2160,7 +2169,7 @@
       </c>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -2169,7 +2178,7 @@
       </c>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:13" ht="42" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -2178,7 +2187,7 @@
       </c>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -2187,20 +2196,20 @@
       </c>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>53</v>
       </c>
       <c r="B7" s="6">
         <f ca="1">NOW()</f>
-        <v>45909.652546180558</v>
+        <v>45964.570907870373</v>
       </c>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>54</v>
       </c>
@@ -2209,7 +2218,7 @@
       <c r="I9" s="11"/>
       <c r="K9" s="11"/>
     </row>
-    <row r="10" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>55</v>
       </c>
@@ -2221,7 +2230,7 @@
       <c r="I10" s="11"/>
       <c r="K10" s="11"/>
     </row>
-    <row r="12" spans="1:13" s="13" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:13" s="13" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>57</v>
       </c>
@@ -2262,7 +2271,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="44.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:13" ht="44.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>70</v>
       </c>
@@ -2303,7 +2312,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="14" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="49" t="s">
         <v>81</v>
       </c>
@@ -2320,7 +2329,7 @@
       <c r="K14" s="21"/>
       <c r="M14" s="22"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="D15" s="5"/>
@@ -2349,30 +2358,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:X28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="41.5" style="5" customWidth="1"/>
+    <col min="2" max="2" width="41.44140625" style="5" customWidth="1"/>
     <col min="3" max="3" width="42.6640625" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" style="23" customWidth="1"/>
-    <col min="5" max="5" width="41.5" style="5" customWidth="1"/>
-    <col min="6" max="6" width="41.1640625" style="22" customWidth="1"/>
-    <col min="7" max="7" width="14.5" style="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" style="23" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="41.109375" style="22" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" style="24" customWidth="1"/>
     <col min="8" max="8" width="12" style="25" customWidth="1"/>
-    <col min="9" max="9" width="20.1640625" customWidth="1"/>
+    <col min="9" max="9" width="20.109375" customWidth="1"/>
     <col min="10" max="11" width="21" customWidth="1"/>
-    <col min="12" max="12" width="27.5" customWidth="1"/>
+    <col min="12" max="12" width="27.44140625" customWidth="1"/>
     <col min="13" max="15" width="26" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="34.33203125" customWidth="1"/>
     <col min="17" max="17" width="36" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="34.83203125" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="34.83203125" customWidth="1"/>
-    <col min="20" max="22" width="28.1640625" style="5" customWidth="1"/>
-    <col min="23" max="23" width="16.1640625" customWidth="1"/>
-    <col min="1021" max="1025" width="11.5" customWidth="1"/>
+    <col min="18" max="18" width="34.77734375" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="34.77734375" customWidth="1"/>
+    <col min="20" max="22" width="28.109375" style="5" customWidth="1"/>
+    <col min="23" max="23" width="16.109375" customWidth="1"/>
+    <col min="1021" max="1025" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -2383,7 +2392,7 @@
       <c r="P1" s="5"/>
       <c r="S1" s="5"/>
     </row>
-    <row r="3" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>85</v>
       </c>
@@ -2398,12 +2407,12 @@
       <c r="U3" s="11"/>
       <c r="V3" s="11"/>
     </row>
-    <row r="4" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="29"/>
       <c r="G4" s="30"/>
       <c r="Q4" s="5"/>
     </row>
-    <row r="5" spans="1:24" s="14" customFormat="1" ht="70" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:24" s="14" customFormat="1" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>86</v>
       </c>
@@ -2468,7 +2477,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="33" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:24" s="33" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>107</v>
       </c>
@@ -2490,7 +2499,7 @@
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
     </row>
-    <row r="7" spans="1:24" ht="42" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:24" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
         <v>70</v>
       </c>
@@ -2564,7 +2573,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="42" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:24" s="42" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="42" t="s">
         <v>133</v>
       </c>
@@ -2577,7 +2586,7 @@
       <c r="U8" s="46"/>
       <c r="V8" s="46"/>
     </row>
-    <row r="9" spans="1:24" ht="32" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:24" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="str">
         <f>CONCATENATE(B9,"#",C9)</f>
         <v>hri:DatasetSeriesShape#dcatap:applicableLegislation</v>
@@ -2606,7 +2615,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="32" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:24" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A10" s="47" t="str">
         <f>CONCATENATE(B10,"#",C10)</f>
         <v>hri:DatasetSeriesShape#dcat:contactPoint</v>
@@ -2639,9 +2648,9 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="16" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:24" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="str">
-        <f t="shared" ref="A11:A18" si="0">CONCATENATE(B11,"#",C11)</f>
+        <f t="shared" ref="A11:A19" si="0">CONCATENATE(B11,"#",C11)</f>
         <v>hri:DatasetSeriesShape#dct:description</v>
       </c>
       <c r="B11" s="49" t="s">
@@ -2674,7 +2683,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="16" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:24" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A12" s="47" t="str">
         <f t="shared" si="0"/>
         <v>hri:DatasetSeriesShape#dct:accrualPeriodicity</v>
@@ -2707,7 +2716,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="47" t="str">
         <f t="shared" si="0"/>
         <v>hri:DatasetSeriesShape#dct:spatial</v>
@@ -2737,7 +2746,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="32" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:24" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A14" s="47" t="str">
         <f t="shared" si="0"/>
         <v>hri:DatasetSeriesShape#dct:modified</v>
@@ -2775,7 +2784,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:24" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" s="47" t="str">
         <f t="shared" si="0"/>
         <v>hri:DatasetSeriesShape#dct:publisher</v>
@@ -2808,7 +2817,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:24" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A16" s="47" t="str">
         <f t="shared" si="0"/>
         <v>hri:DatasetSeriesShape#dct:issued</v>
@@ -2845,7 +2854,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:24" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A17" s="47" t="str">
         <f t="shared" si="0"/>
         <v>hri:DatasetSeriesShape#dct:temporal</v>
@@ -2874,7 +2883,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:24" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A18" s="47" t="str">
         <f t="shared" si="0"/>
         <v>hri:DatasetSeriesShape#dct:title</v>
@@ -2909,15 +2918,36 @@
         <v>151</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="15" x14ac:dyDescent="0.15">
-      <c r="A19" s="47"/>
-      <c r="B19" s="49"/>
+    <row r="19" spans="1:24" ht="105.6" x14ac:dyDescent="0.25">
+      <c r="A19" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>hri:DatasetSeriesShape#dcat:seriesMember</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="55" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>180</v>
+      </c>
       <c r="G19" s="52"/>
-      <c r="J19" s="54"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-    </row>
-    <row r="20" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+      <c r="I19" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="S19" s="5"/>
+      <c r="W19" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="X19" s="48" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A20" s="47"/>
       <c r="B20" s="49"/>
       <c r="G20" s="52"/>
@@ -2926,7 +2956,7 @@
       <c r="W20" s="48"/>
       <c r="X20" s="48"/>
     </row>
-    <row r="21" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:24" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A21" s="47"/>
       <c r="B21" s="49"/>
       <c r="C21" s="55"/>
@@ -2938,7 +2968,7 @@
       <c r="W21" s="48"/>
       <c r="X21" s="48"/>
     </row>
-    <row r="22" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:24" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A22" s="47"/>
       <c r="B22" s="49"/>
       <c r="C22" s="55"/>
@@ -2949,7 +2979,7 @@
       <c r="W22" s="48"/>
       <c r="X22" s="48"/>
     </row>
-    <row r="23" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:24" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A23" s="47"/>
       <c r="B23" s="49"/>
       <c r="C23" s="58"/>
@@ -2961,7 +2991,7 @@
       <c r="W23" s="48"/>
       <c r="X23" s="48"/>
     </row>
-    <row r="24" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:24" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A24" s="47"/>
       <c r="B24" s="49"/>
       <c r="C24" s="55"/>
@@ -2973,7 +3003,7 @@
       <c r="W24" s="48"/>
       <c r="X24" s="48"/>
     </row>
-    <row r="25" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:24" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A25" s="47"/>
       <c r="B25" s="49"/>
       <c r="D25" s="55"/>
@@ -2983,7 +3013,7 @@
       <c r="W25" s="48"/>
       <c r="X25" s="48"/>
     </row>
-    <row r="26" spans="1:24" ht="15" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:24" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A26" s="47"/>
       <c r="B26" s="49"/>
       <c r="D26" s="55"/>
@@ -2994,11 +3024,11 @@
       <c r="W26" s="48"/>
       <c r="X26" s="48"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="47"/>
       <c r="B27" s="49"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="47"/>
       <c r="B28" s="49"/>
     </row>
@@ -3035,45 +3065,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A70A77E-587D-3A4A-A435-6E45C6479C4C}">
   <dimension ref="A7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="7" ht="13" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="7" ht="13.05" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e" xsi:nil="true"/>
-    <Categorie xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="221af607-abea-4d5e-830c-567dcc03c0ec" xsi:nil="true"/>
-    <Persoon xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Persoon>
-    <Opmerkingen xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000B1A1CF98C819F4881BB4349588D0C85" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="31f6c59cfd598d1d7de5b45c1822abcd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cfc87205-1831-4b6c-a7b4-76d40079a43e" xmlns:ns3="221af607-abea-4d5e-830c-567dcc03c0ec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="67714481eaab3d0eef8b708c465ce66d" ns2:_="" ns3:_="">
     <xsd:import namespace="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
@@ -3361,32 +3361,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C2A762-C9A0-490C-9DDC-F35C0AECA17E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="221af607-abea-4d5e-830c-567dcc03c0ec"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CE3AE30-F94D-4B2D-A964-81B3B3999808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e" xsi:nil="true"/>
+    <Categorie xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="221af607-abea-4d5e-830c-567dcc03c0ec" xsi:nil="true"/>
+    <Persoon xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Persoon>
+    <Opmerkingen xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B1F0054-1087-48F4-9119-4B6CD5EB6A99}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3403,4 +3408,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CE3AE30-F94D-4B2D-A964-81B3B3999808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C2A762-C9A0-490C-9DDC-F35C0AECA17E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="221af607-abea-4d5e-830c-567dcc03c0ec"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>